--- a/data/raw/2026-07-08_HV.xlsx
+++ b/data/raw/2026-07-08_HV.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
         <v>135</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
         <v>134</v>
@@ -714,34 +714,38 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CONSPIRATOR</t>
+          <t>CONSPIRATOR(Scratched)</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9/10/12/13/8/5</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P5" t="n">
         <v>20</v>
       </c>
@@ -776,7 +780,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>132</v>
@@ -834,7 +838,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>131</v>
@@ -1008,7 +1012,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
         <v>129</v>
@@ -1066,7 +1070,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>129</v>
@@ -1124,7 +1128,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>128</v>
@@ -1265,7 +1269,7 @@
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1323,7 +1327,7 @@
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="16">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="17">
@@ -1439,7 +1443,7 @@
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1497,7 +1501,7 @@
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1675,7 @@
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="22">
@@ -1729,7 +1733,7 @@
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
@@ -1787,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="24">
@@ -1845,7 +1849,7 @@
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -1965,7 +1969,7 @@
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -2023,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="28">
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -2313,7 +2317,7 @@
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
@@ -2371,7 +2375,7 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="34">
@@ -2429,7 +2433,7 @@
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
@@ -2487,7 +2491,7 @@
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="36">
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -2661,7 +2665,7 @@
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -2719,7 +2723,7 @@
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="40">
@@ -2777,7 +2781,7 @@
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="41">
@@ -2835,7 +2839,7 @@
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -2893,7 +2897,7 @@
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -3009,7 +3013,7 @@
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45">
@@ -3067,7 +3071,7 @@
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="46">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -3183,7 +3187,7 @@
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="48">
@@ -3241,7 +3245,7 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="49">
@@ -3299,7 +3303,7 @@
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -3357,7 +3361,7 @@
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
@@ -3473,7 +3477,7 @@
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
@@ -3531,7 +3535,7 @@
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="54">
@@ -3589,7 +3593,7 @@
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
@@ -3647,7 +3651,7 @@
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="56">
@@ -3705,7 +3709,7 @@
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -3821,7 +3825,7 @@
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -3879,7 +3883,7 @@
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="60">
@@ -3937,7 +3941,7 @@
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="61">
@@ -3995,7 +3999,7 @@
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -4053,7 +4057,7 @@
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
@@ -4169,7 +4173,7 @@
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="65">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="66">
@@ -4285,7 +4289,7 @@
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67">
@@ -4343,7 +4347,7 @@
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="68">
@@ -4401,7 +4405,7 @@
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69">
@@ -4517,7 +4521,7 @@
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="72">
@@ -4633,7 +4637,7 @@
       </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="73">
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74">
@@ -4749,7 +4753,7 @@
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -4865,7 +4869,7 @@
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77">
@@ -4923,7 +4927,7 @@
       </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="78">
@@ -4981,7 +4985,7 @@
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79">
@@ -5039,7 +5043,7 @@
       </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="80">
@@ -5097,7 +5101,7 @@
       </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81">
@@ -5217,7 +5221,7 @@
       </c>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
@@ -5275,7 +5279,7 @@
       </c>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="84">
@@ -5333,7 +5337,7 @@
       </c>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="85">
@@ -5391,7 +5395,7 @@
       </c>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -5565,7 +5569,7 @@
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89">
@@ -5623,7 +5627,7 @@
       </c>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="90">
@@ -5681,7 +5685,7 @@
       </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="91">
@@ -5739,7 +5743,7 @@
       </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="92">
@@ -5797,7 +5801,7 @@
       </c>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
@@ -5913,7 +5917,7 @@
       </c>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -5971,7 +5975,7 @@
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="96">
@@ -6029,7 +6033,7 @@
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="97">
@@ -6087,7 +6091,7 @@
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
@@ -6145,7 +6149,7 @@
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99">
@@ -6261,7 +6265,7 @@
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101">
@@ -6319,7 +6323,7 @@
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="102">
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103">
@@ -6439,7 +6443,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="104">
@@ -6497,7 +6501,7 @@
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105">
@@ -6555,7 +6559,7 @@
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6686,7 +6690,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -6740,10 +6744,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -6794,7 +6798,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.9</v>
@@ -6848,11 +6852,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -6902,10 +6904,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -6959,7 +6961,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -7010,7 +7012,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
@@ -7064,10 +7066,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -7118,10 +7120,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -7176,10 +7178,10 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -7230,10 +7232,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -7284,10 +7286,10 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -15386,7 +15388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15426,14 +15428,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>2.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15447,14 +15449,14 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15468,14 +15470,14 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15485,18 +15487,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15506,18 +15508,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15527,18 +15529,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15548,18 +15550,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>6.9</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15569,18 +15571,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9.1</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15590,18 +15592,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>5.9</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15611,18 +15613,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15632,39 +15634,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27</v>
+        <v>9.9</v>
       </c>
       <c r="D12" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15674,18 +15676,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15695,18 +15697,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15716,18 +15718,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15737,18 +15739,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15758,18 +15760,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15779,18 +15781,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>6.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15800,18 +15802,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15821,18 +15823,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.1</v>
+        <v>5.9</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15842,18 +15844,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15863,60 +15865,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>9.9</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9.9</v>
+        <v>4.1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15926,18 +15928,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15947,18 +15949,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="D27" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15968,18 +15970,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -15989,18 +15991,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16010,18 +16012,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>6.9</v>
       </c>
       <c r="D30" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16031,18 +16033,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D31" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16052,18 +16054,18 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="D32" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16073,18 +16075,18 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9.1</v>
+        <v>18</v>
       </c>
       <c r="D33" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16094,81 +16096,81 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>45</v>
+        <v>9.9</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>27</v>
+        <v>4.1</v>
       </c>
       <c r="D36" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9.9</v>
+        <v>4.5</v>
       </c>
       <c r="D37" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16178,18 +16180,18 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9.5</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16199,18 +16201,18 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="D39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16220,18 +16222,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4.2</v>
+        <v>37</v>
       </c>
       <c r="D40" t="n">
-        <v>1.9</v>
+        <v>7.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16241,18 +16243,18 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>30</v>
+        <v>6.9</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>2.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16262,18 +16264,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="D42" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16283,18 +16285,18 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="D43" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16304,18 +16306,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D44" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16325,102 +16327,102 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="D45" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="D47" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>27</v>
+        <v>4.5</v>
       </c>
       <c r="D48" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9.9</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16430,18 +16432,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="D50" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16451,18 +16453,18 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.1</v>
+        <v>37</v>
       </c>
       <c r="D51" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16472,18 +16474,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
       <c r="D52" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16493,18 +16495,18 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16514,18 +16516,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="D54" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16535,18 +16537,18 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16556,123 +16558,123 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="D56" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>45</v>
+        <v>4.1</v>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="D59" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D60" t="n">
-        <v>7.1</v>
+        <v>4.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9.9</v>
+        <v>13</v>
       </c>
       <c r="D61" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16682,18 +16684,18 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9.5</v>
+        <v>37</v>
       </c>
       <c r="D62" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16703,18 +16705,18 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="D63" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16724,18 +16726,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4.2</v>
+        <v>56</v>
       </c>
       <c r="D64" t="n">
-        <v>1.9</v>
+        <v>12</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16745,18 +16747,18 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>30</v>
+        <v>5.9</v>
       </c>
       <c r="D65" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16766,18 +16768,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D66" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16787,144 +16789,144 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="D67" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D68" t="n">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>9.1</v>
+        <v>4.1</v>
       </c>
       <c r="D69" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>45</v>
+        <v>4.5</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>1.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D71" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D72" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>9.9</v>
+        <v>37</v>
       </c>
       <c r="D73" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16934,18 +16936,18 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9.5</v>
+        <v>6.9</v>
       </c>
       <c r="D74" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16955,18 +16957,18 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5.1</v>
+        <v>56</v>
       </c>
       <c r="D75" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16976,18 +16978,18 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="D76" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -16997,18 +16999,18 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17018,165 +17020,165 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="D78" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="D80" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9.1</v>
+        <v>4.5</v>
       </c>
       <c r="D81" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D82" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D83" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D84" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9.9</v>
+        <v>6.9</v>
       </c>
       <c r="D85" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17186,18 +17188,18 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9.5</v>
+        <v>56</v>
       </c>
       <c r="D86" t="n">
-        <v>2.7</v>
+        <v>12</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17207,18 +17209,18 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="D87" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17228,18 +17230,18 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="D88" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17249,186 +17251,186 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D90" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="D91" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="D92" t="n">
-        <v>7.5</v>
+        <v>1.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9.1</v>
+        <v>14</v>
       </c>
       <c r="D93" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="D95" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>27</v>
+        <v>6.9</v>
       </c>
       <c r="D96" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9.9</v>
+        <v>56</v>
       </c>
       <c r="D97" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17438,18 +17440,18 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>9.5</v>
+        <v>5.9</v>
       </c>
       <c r="D98" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17459,18 +17461,18 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="D99" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17480,207 +17482,207 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
+        <v>11</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
         <v>10</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>30</v>
-      </c>
       <c r="D101" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="D102" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="D103" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D104" t="n">
-        <v>7.5</v>
+        <v>4.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="D105" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="D107" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="D108" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9.9</v>
+        <v>5.9</v>
       </c>
       <c r="D109" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17690,18 +17692,18 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9.5</v>
+        <v>18</v>
       </c>
       <c r="D110" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17711,228 +17713,228 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="D111" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>30</v>
+        <v>4.1</v>
       </c>
       <c r="D113" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="D114" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D115" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D116" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>9.1</v>
+        <v>37</v>
       </c>
       <c r="D117" t="n">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>45</v>
+        <v>6.9</v>
       </c>
       <c r="D118" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D119" t="n">
-        <v>1.2</v>
+        <v>12</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>27</v>
+        <v>5.9</v>
       </c>
       <c r="D120" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>9.9</v>
+        <v>18</v>
       </c>
       <c r="D121" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -17942,249 +17944,18 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="D122" t="n">
         <v>2.7</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>12</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D123" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>12</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D124" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>12</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>30</v>
-      </c>
-      <c r="D125" t="n">
-        <v>11</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>12</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>13</v>
-      </c>
-      <c r="D126" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>12</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>13</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>12</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>16</v>
-      </c>
-      <c r="D128" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>12</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="D129" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>12</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>45</v>
-      </c>
-      <c r="D130" t="n">
-        <v>11</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>12</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>6</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>12</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>27</v>
-      </c>
-      <c r="D132" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>12</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="D133" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>12:52:03</t>
+          <t>12:18:27</t>
         </is>
       </c>
     </row>
@@ -18286,7 +18057,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>135</v>
@@ -18317,7 +18088,7 @@
         <v>12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="3">
@@ -18337,7 +18108,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>134</v>
@@ -18368,7 +18139,7 @@
         <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -18435,34 +18206,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CONSPIRATOR</t>
+          <t>CONSPIRATOR(Scratched)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L Hewitson</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B Crawford</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9/10/12/13/8/5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="K5" t="n">
         <v>20</v>
       </c>
@@ -18470,7 +18245,7 @@
         <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="6">
@@ -18490,7 +18265,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>132</v>
@@ -18521,7 +18296,7 @@
         <v>12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7">
@@ -18541,7 +18316,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>131</v>
@@ -18572,7 +18347,7 @@
         <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -18694,7 +18469,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>129</v>
@@ -18725,7 +18500,7 @@
         <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -18745,7 +18520,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>129</v>
@@ -18776,7 +18551,7 @@
         <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -18796,7 +18571,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>128</v>
@@ -18827,7 +18602,7 @@
         <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="13">
@@ -19009,7 +18784,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -19063,10 +18838,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -19117,10 +18892,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -19171,11 +18946,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -19225,10 +18998,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -19282,7 +19055,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -19333,10 +19106,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -19387,10 +19160,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -19441,10 +19214,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -19495,10 +19268,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -19549,10 +19322,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -19610,7 +19383,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -19747,7 +19520,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -19801,10 +19574,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -19855,10 +19628,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -19909,11 +19682,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -19963,10 +19734,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -20020,7 +19791,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -20071,10 +19842,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -20125,10 +19896,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -20179,10 +19950,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -20233,10 +20004,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -20287,10 +20058,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -20344,7 +20115,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -20481,7 +20252,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -20535,10 +20306,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>8</v>
@@ -20589,7 +20360,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.9</v>
@@ -20643,11 +20414,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>8</v>
       </c>
@@ -20697,10 +20466,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>8</v>
@@ -20754,7 +20523,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>8</v>
@@ -20805,10 +20574,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
@@ -20859,10 +20628,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>8</v>
@@ -20999,7 +20768,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -21053,10 +20822,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -21107,10 +20876,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -21161,11 +20930,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -21215,10 +20982,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -21272,7 +21039,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -21323,7 +21090,7 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
@@ -21377,10 +21144,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -21431,10 +21198,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -21485,10 +21252,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -21539,10 +21306,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -21596,7 +21363,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -21733,7 +21500,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -21787,10 +21554,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -21841,7 +21608,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.9</v>
@@ -21895,11 +21662,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -21949,10 +21714,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -22006,7 +21771,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -22057,10 +21822,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -22111,10 +21876,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -22165,10 +21930,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -22219,10 +21984,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -22273,10 +22038,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -22330,7 +22095,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -22467,7 +22232,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -22521,10 +22286,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -22575,10 +22340,10 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
         <v>12</v>
@@ -22629,11 +22394,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -22683,10 +22446,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -22740,7 +22503,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -22791,10 +22554,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -22845,10 +22608,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -22899,10 +22662,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -22953,10 +22716,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -23007,10 +22770,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -23068,7 +22831,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
@@ -23205,7 +22968,7 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
         <v>2.7</v>
@@ -23259,10 +23022,10 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -23313,7 +23076,7 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.9</v>
@@ -23367,11 +23130,9 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>12</v>
       </c>
@@ -23421,10 +23182,10 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -23478,7 +23239,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
         <v>12</v>
@@ -23529,10 +23290,10 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L8" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
@@ -23583,10 +23344,10 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
         <v>12</v>
@@ -23637,10 +23398,10 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
         <v>12</v>
@@ -23691,10 +23452,10 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
@@ -23745,10 +23506,10 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="M12" t="n">
         <v>12</v>
@@ -23802,7 +23563,7 @@
         <v>9.9</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>12</v>
